--- a/Mercury 1.0.xlsx
+++ b/Mercury 1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lizar\OneDrive\Documentos\Python programas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{113A0F3D-05DF-4324-82E7-40CD86EB604F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD4185A8-FA86-4FC1-8350-FAA047FD21C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Mercury 1.0.xlsx
+++ b/Mercury 1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lizar\OneDrive\Documentos\Python programas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD4185A8-FA86-4FC1-8350-FAA047FD21C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CD9661D-7A81-4D5C-9F6F-CC5C2A194424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11061,11 +11061,11 @@
     <row r="69" spans="1:2">
       <c r="A69" s="2">
         <f>Sheet1!A:A</f>
-        <v>0</v>
-      </c>
-      <c r="B69" s="6">
+        <v>46120</v>
+      </c>
+      <c r="B69" s="5">
         <f>Sheet1!H:H</f>
-        <v>0</v>
+        <v>0.49700000000000033</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -15584,7 +15584,7 @@
         <v>3.44</v>
       </c>
       <c r="H38" s="21">
-        <f t="shared" ref="H38:H68" si="2">+F38-G38</f>
+        <f t="shared" ref="H38:H69" si="2">+F38-G38</f>
         <v>0.58700000000000019</v>
       </c>
       <c r="I38" s="39">
@@ -17006,7 +17006,7 @@
         <v>46119</v>
       </c>
       <c r="B68" s="18">
-        <v>6611.83</v>
+        <v>6616.85</v>
       </c>
       <c r="C68" s="18">
         <v>24202.37</v>
@@ -17037,7 +17037,7 @@
         <v>0.85570000000000002</v>
       </c>
       <c r="L68" s="18">
-        <v>96.28</v>
+        <v>112.95</v>
       </c>
       <c r="M68" s="18">
         <v>4860.8500000000004</v>
@@ -17050,21 +17050,52 @@
       </c>
     </row>
     <row r="69" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A69" s="42"/>
-      <c r="B69" s="18"/>
-      <c r="C69" s="18"/>
-      <c r="D69" s="18"/>
-      <c r="E69" s="18"/>
-      <c r="F69" s="43"/>
-      <c r="G69" s="44"/>
-      <c r="H69" s="47"/>
-      <c r="I69" s="45"/>
-      <c r="J69" s="18"/>
-      <c r="K69" s="46"/>
-      <c r="L69" s="18"/>
-      <c r="M69" s="18"/>
-      <c r="N69" s="44"/>
-      <c r="O69" s="44"/>
+      <c r="A69" s="42">
+        <v>46120</v>
+      </c>
+      <c r="B69" s="18">
+        <v>6782.81</v>
+      </c>
+      <c r="C69" s="18">
+        <v>24903.17</v>
+      </c>
+      <c r="D69" s="18">
+        <v>47906.92</v>
+      </c>
+      <c r="E69" s="18">
+        <v>4458.34</v>
+      </c>
+      <c r="F69" s="43">
+        <v>4.2910000000000004</v>
+      </c>
+      <c r="G69" s="44">
+        <v>3.794</v>
+      </c>
+      <c r="H69" s="21">
+        <f t="shared" si="2"/>
+        <v>0.49700000000000033</v>
+      </c>
+      <c r="I69" s="45">
+        <v>21.04</v>
+      </c>
+      <c r="J69" s="18">
+        <v>99.13</v>
+      </c>
+      <c r="K69" s="46">
+        <v>0.85770000000000002</v>
+      </c>
+      <c r="L69" s="18">
+        <v>97.1</v>
+      </c>
+      <c r="M69" s="18">
+        <v>4738.7</v>
+      </c>
+      <c r="N69" s="44">
+        <v>475.95800000000003</v>
+      </c>
+      <c r="O69" s="44">
+        <v>73.795000000000002</v>
+      </c>
     </row>
     <row r="70" spans="1:15" ht="16.5" customHeight="1">
       <c r="A70" s="42"/>
@@ -35041,7 +35072,7 @@
       </c>
       <c r="B14" s="34">
         <f>Sheet1!B68</f>
-        <v>6611.83</v>
+        <v>6616.85</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -35051,7 +35082,7 @@
       </c>
       <c r="B15" s="34">
         <f>Sheet1!B69</f>
-        <v>0</v>
+        <v>6782.81</v>
       </c>
     </row>
   </sheetData>

--- a/Mercury 1.0.xlsx
+++ b/Mercury 1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lizar\OneDrive\Documentos\Python programas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CD9661D-7A81-4D5C-9F6F-CC5C2A194424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BF1D066-F354-435B-BE34-BAFCE885F195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11071,11 +11071,11 @@
     <row r="70" spans="1:2">
       <c r="A70" s="2">
         <f>Sheet1!A:A</f>
-        <v>0</v>
-      </c>
-      <c r="B70" s="6">
+        <v>46121</v>
+      </c>
+      <c r="B70" s="5">
         <f>Sheet1!H:H</f>
-        <v>0</v>
+        <v>0.49999999999999956</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -15584,7 +15584,7 @@
         <v>3.44</v>
       </c>
       <c r="H38" s="21">
-        <f t="shared" ref="H38:H69" si="2">+F38-G38</f>
+        <f t="shared" ref="H38:H70" si="2">+F38-G38</f>
         <v>0.58700000000000019</v>
       </c>
       <c r="I38" s="39">
@@ -17098,21 +17098,52 @@
       </c>
     </row>
     <row r="70" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A70" s="42"/>
-      <c r="B70" s="18"/>
-      <c r="C70" s="18"/>
-      <c r="D70" s="18"/>
-      <c r="E70" s="18"/>
-      <c r="F70" s="43"/>
-      <c r="G70" s="44"/>
-      <c r="H70" s="47"/>
-      <c r="I70" s="45"/>
-      <c r="J70" s="18"/>
-      <c r="K70" s="46"/>
-      <c r="L70" s="18"/>
-      <c r="M70" s="18"/>
-      <c r="N70" s="44"/>
-      <c r="O70" s="44"/>
+      <c r="A70" s="42">
+        <v>46121</v>
+      </c>
+      <c r="B70" s="18">
+        <v>6824.66</v>
+      </c>
+      <c r="C70" s="18">
+        <v>25082.09</v>
+      </c>
+      <c r="D70" s="18">
+        <v>48185.8</v>
+      </c>
+      <c r="E70" s="18">
+        <v>4452.6499999999996</v>
+      </c>
+      <c r="F70" s="43">
+        <v>4.2889999999999997</v>
+      </c>
+      <c r="G70" s="44">
+        <v>3.7890000000000001</v>
+      </c>
+      <c r="H70" s="21">
+        <f t="shared" si="2"/>
+        <v>0.49999999999999956</v>
+      </c>
+      <c r="I70" s="45">
+        <v>19.489999999999998</v>
+      </c>
+      <c r="J70" s="18">
+        <v>98.9</v>
+      </c>
+      <c r="K70" s="46">
+        <v>0.85550000000000004</v>
+      </c>
+      <c r="L70" s="18">
+        <v>98.48</v>
+      </c>
+      <c r="M70" s="18">
+        <v>4780.3999999999996</v>
+      </c>
+      <c r="N70" s="44">
+        <v>476.43400000000003</v>
+      </c>
+      <c r="O70" s="44">
+        <v>75.78</v>
+      </c>
     </row>
     <row r="71" spans="1:15" ht="16.5" customHeight="1">
       <c r="A71" s="42"/>

--- a/Mercury 1.0.xlsx
+++ b/Mercury 1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lizar\OneDrive\Documentos\Python programas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BF1D066-F354-435B-BE34-BAFCE885F195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D603B820-4E27-4F12-B2CE-8F0242088E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29280" yWindow="480" windowWidth="21600" windowHeight="11235" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="US10 yt" sheetId="1" r:id="rId1"/>
@@ -11081,31 +11081,31 @@
     <row r="71" spans="1:2">
       <c r="A71" s="2">
         <f>Sheet1!A:A</f>
-        <v>0</v>
-      </c>
-      <c r="B71" s="6">
+        <v>46122</v>
+      </c>
+      <c r="B71" s="5">
         <f>Sheet1!H:H</f>
-        <v>0</v>
+        <v>0.51600000000000001</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
         <f>Sheet1!A:A</f>
-        <v>0</v>
-      </c>
-      <c r="B72" s="6">
+        <v>46125</v>
+      </c>
+      <c r="B72" s="5">
         <f>Sheet1!H:H</f>
-        <v>0</v>
+        <v>0.51599999999999957</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
         <f>Sheet1!A:A</f>
-        <v>0</v>
-      </c>
-      <c r="B73" s="6">
+        <v>46126</v>
+      </c>
+      <c r="B73" s="5">
         <f>Sheet1!H:H</f>
-        <v>0</v>
+        <v>0.50500000000000034</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -15584,7 +15584,7 @@
         <v>3.44</v>
       </c>
       <c r="H38" s="21">
-        <f t="shared" ref="H38:H70" si="2">+F38-G38</f>
+        <f t="shared" ref="H38:H73" si="2">+F38-G38</f>
         <v>0.58700000000000019</v>
       </c>
       <c r="I38" s="39">
@@ -17146,55 +17146,148 @@
       </c>
     </row>
     <row r="71" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A71" s="42"/>
-      <c r="B71" s="18"/>
-      <c r="C71" s="18"/>
-      <c r="D71" s="18"/>
-      <c r="E71" s="18"/>
-      <c r="F71" s="43"/>
-      <c r="G71" s="44"/>
-      <c r="H71" s="47"/>
-      <c r="I71" s="45"/>
-      <c r="J71" s="18"/>
-      <c r="K71" s="46"/>
-      <c r="L71" s="18"/>
-      <c r="M71" s="18"/>
-      <c r="N71" s="44"/>
-      <c r="O71" s="44"/>
+      <c r="A71" s="42">
+        <v>46122</v>
+      </c>
+      <c r="B71" s="18">
+        <v>6816.89</v>
+      </c>
+      <c r="C71" s="18">
+        <v>25116.34</v>
+      </c>
+      <c r="D71" s="18">
+        <v>47916.57</v>
+      </c>
+      <c r="E71" s="18">
+        <v>4473.96</v>
+      </c>
+      <c r="F71" s="43">
+        <v>4.3170000000000002</v>
+      </c>
+      <c r="G71" s="44">
+        <v>3.8010000000000002</v>
+      </c>
+      <c r="H71" s="21">
+        <f t="shared" si="2"/>
+        <v>0.51600000000000001</v>
+      </c>
+      <c r="I71" s="45">
+        <v>19.23</v>
+      </c>
+      <c r="J71" s="18">
+        <v>98.65</v>
+      </c>
+      <c r="K71" s="46">
+        <v>0.85329999999999995</v>
+      </c>
+      <c r="L71" s="18">
+        <v>96.57</v>
+      </c>
+      <c r="M71" s="18">
+        <v>4787.3999999999996</v>
+      </c>
+      <c r="N71" s="44">
+        <v>477.149</v>
+      </c>
+      <c r="O71" s="44">
+        <v>76.48</v>
+      </c>
     </row>
     <row r="72" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A72" s="42"/>
-      <c r="B72" s="18"/>
-      <c r="C72" s="18"/>
-      <c r="D72" s="18"/>
-      <c r="E72" s="18"/>
-      <c r="F72" s="43"/>
-      <c r="G72" s="44"/>
-      <c r="H72" s="47"/>
-      <c r="I72" s="45"/>
-      <c r="J72" s="18"/>
-      <c r="K72" s="46"/>
-      <c r="L72" s="18"/>
-      <c r="M72" s="18"/>
-      <c r="N72" s="44"/>
-      <c r="O72" s="44"/>
+      <c r="A72" s="42">
+        <v>46125</v>
+      </c>
+      <c r="B72" s="18">
+        <v>6886.24</v>
+      </c>
+      <c r="C72" s="18">
+        <v>25383.72</v>
+      </c>
+      <c r="D72" s="18">
+        <v>48218.25</v>
+      </c>
+      <c r="E72" s="18">
+        <v>4503.84</v>
+      </c>
+      <c r="F72" s="43">
+        <v>4.2969999999999997</v>
+      </c>
+      <c r="G72" s="44">
+        <v>3.7810000000000001</v>
+      </c>
+      <c r="H72" s="21">
+        <f t="shared" si="2"/>
+        <v>0.51599999999999957</v>
+      </c>
+      <c r="I72" s="45">
+        <v>19.12</v>
+      </c>
+      <c r="J72" s="18">
+        <v>98.37</v>
+      </c>
+      <c r="K72" s="46">
+        <v>0.8498</v>
+      </c>
+      <c r="L72" s="18">
+        <v>96.57</v>
+      </c>
+      <c r="M72" s="18">
+        <v>4781.47</v>
+      </c>
+      <c r="N72" s="44">
+        <v>477.62599999999998</v>
+      </c>
+      <c r="O72" s="44">
+        <v>75.935000000000002</v>
+      </c>
     </row>
     <row r="73" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A73" s="42"/>
-      <c r="B73" s="18"/>
-      <c r="C73" s="18"/>
-      <c r="D73" s="18"/>
-      <c r="E73" s="18"/>
-      <c r="F73" s="43"/>
-      <c r="G73" s="44"/>
-      <c r="H73" s="47"/>
-      <c r="I73" s="45"/>
-      <c r="J73" s="18"/>
-      <c r="K73" s="46"/>
-      <c r="L73" s="18"/>
-      <c r="M73" s="18"/>
-      <c r="N73" s="44"/>
-      <c r="O73" s="44"/>
+      <c r="A73" s="42">
+        <v>46126</v>
+      </c>
+      <c r="B73" s="18">
+        <v>6967.38</v>
+      </c>
+      <c r="C73" s="18">
+        <v>25842</v>
+      </c>
+      <c r="D73" s="18">
+        <v>48535.99</v>
+      </c>
+      <c r="E73" s="18">
+        <v>4563.68</v>
+      </c>
+      <c r="F73" s="43">
+        <v>4.2560000000000002</v>
+      </c>
+      <c r="G73" s="44">
+        <v>3.7509999999999999</v>
+      </c>
+      <c r="H73" s="21">
+        <f t="shared" si="2"/>
+        <v>0.50500000000000034</v>
+      </c>
+      <c r="I73" s="45">
+        <v>18.36</v>
+      </c>
+      <c r="J73" s="18">
+        <v>98.12</v>
+      </c>
+      <c r="K73" s="46">
+        <v>0.8478</v>
+      </c>
+      <c r="L73" s="18">
+        <v>90.3</v>
+      </c>
+      <c r="M73" s="18">
+        <v>4861.95</v>
+      </c>
+      <c r="N73" s="44">
+        <v>478.58100000000002</v>
+      </c>
+      <c r="O73" s="44">
+        <v>79.628</v>
+      </c>
     </row>
     <row r="74" spans="1:15" ht="16.5" customHeight="1">
       <c r="A74" s="42"/>

--- a/Mercury 1.0.xlsx
+++ b/Mercury 1.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lizar\OneDrive\Documentos\Python programas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7cb8230cb7254a08/Documentos/Python programas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{818A56B8-C8EB-4906-B8FD-CEC95D79D036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE456156-06C9-4620-8F0F-EA061AE31D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3612" yWindow="924" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30195" yWindow="1395" windowWidth="21600" windowHeight="11235" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="US10 yt" sheetId="1" r:id="rId1"/>
@@ -97,7 +97,7 @@
     <t>Bs/Usd ( tasa oficial)</t>
   </si>
   <si>
-    <t xml:space="preserve">Silver </t>
+    <t>SIlver USD/Oz</t>
   </si>
   <si>
     <t>4:</t>
@@ -464,16 +464,16 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="5"/>
-          <bgColor theme="5"/>
+          <fgColor rgb="FF93C47D"/>
+          <bgColor rgb="FF93C47D"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF57BB8A"/>
-          <bgColor rgb="FF57BB8A"/>
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -11168,21 +11168,21 @@
     <row r="80" spans="1:2">
       <c r="A80" s="2">
         <f>Sheet1!A:A</f>
-        <v>0</v>
-      </c>
-      <c r="B80" s="6">
+        <v>46135</v>
+      </c>
+      <c r="B80" s="5">
         <f>Sheet1!H:H</f>
-        <v>0</v>
+        <v>0.49800000000000022</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
         <f>Sheet1!A:A</f>
-        <v>0</v>
-      </c>
-      <c r="B81" s="6">
+        <v>46136</v>
+      </c>
+      <c r="B81" s="5">
         <f>Sheet1!H:H</f>
-        <v>0</v>
+        <v>0.52700000000000058</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -15581,7 +15581,7 @@
         <v>3.44</v>
       </c>
       <c r="H38" s="21">
-        <f t="shared" ref="H38:H79" si="2">+F38-G38</f>
+        <f t="shared" ref="H38:H81" si="2">+F38-G38</f>
         <v>0.58700000000000019</v>
       </c>
       <c r="I38" s="39">
@@ -17575,38 +17575,100 @@
       </c>
     </row>
     <row r="80" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A80" s="42"/>
-      <c r="B80" s="18"/>
-      <c r="C80" s="18"/>
-      <c r="D80" s="18"/>
-      <c r="E80" s="18"/>
-      <c r="F80" s="43"/>
-      <c r="G80" s="44"/>
-      <c r="H80" s="47"/>
-      <c r="I80" s="45"/>
-      <c r="J80" s="18"/>
-      <c r="K80" s="46"/>
-      <c r="L80" s="18"/>
-      <c r="M80" s="18"/>
-      <c r="N80" s="44"/>
-      <c r="O80" s="44"/>
+      <c r="A80" s="42">
+        <v>46135</v>
+      </c>
+      <c r="B80" s="18">
+        <v>7108.4</v>
+      </c>
+      <c r="C80" s="18">
+        <v>26782.63</v>
+      </c>
+      <c r="D80" s="18">
+        <v>49310.32</v>
+      </c>
+      <c r="E80" s="18">
+        <v>4613.01</v>
+      </c>
+      <c r="F80" s="43">
+        <v>4.3230000000000004</v>
+      </c>
+      <c r="G80" s="44">
+        <v>3.8250000000000002</v>
+      </c>
+      <c r="H80" s="21">
+        <f t="shared" si="2"/>
+        <v>0.49800000000000022</v>
+      </c>
+      <c r="I80" s="45">
+        <v>19.309999999999999</v>
+      </c>
+      <c r="J80" s="18">
+        <v>98.77</v>
+      </c>
+      <c r="K80" s="46">
+        <v>0.85589999999999999</v>
+      </c>
+      <c r="L80" s="18">
+        <v>96.81</v>
+      </c>
+      <c r="M80" s="18">
+        <v>4710.8599999999997</v>
+      </c>
+      <c r="N80" s="44">
+        <v>483.87</v>
+      </c>
+      <c r="O80" s="44">
+        <v>75.454999999999998</v>
+      </c>
     </row>
     <row r="81" spans="1:15" ht="16.5" customHeight="1">
-      <c r="A81" s="42"/>
-      <c r="B81" s="18"/>
-      <c r="C81" s="18"/>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
-      <c r="F81" s="43"/>
-      <c r="G81" s="44"/>
-      <c r="H81" s="47"/>
-      <c r="I81" s="45"/>
-      <c r="J81" s="18"/>
-      <c r="K81" s="46"/>
-      <c r="L81" s="18"/>
-      <c r="M81" s="18"/>
-      <c r="N81" s="44"/>
-      <c r="O81" s="44"/>
+      <c r="A81" s="42">
+        <v>46136</v>
+      </c>
+      <c r="B81" s="18">
+        <v>7164.73</v>
+      </c>
+      <c r="C81" s="18">
+        <v>27303.67</v>
+      </c>
+      <c r="D81" s="18">
+        <v>49229.48</v>
+      </c>
+      <c r="E81" s="18">
+        <v>4634.45</v>
+      </c>
+      <c r="F81" s="43">
+        <v>4.3070000000000004</v>
+      </c>
+      <c r="G81" s="44">
+        <v>3.78</v>
+      </c>
+      <c r="H81" s="21">
+        <f t="shared" si="2"/>
+        <v>0.52700000000000058</v>
+      </c>
+      <c r="I81" s="45">
+        <v>18.62</v>
+      </c>
+      <c r="J81" s="18">
+        <v>98.53</v>
+      </c>
+      <c r="K81" s="46">
+        <v>0.85329999999999995</v>
+      </c>
+      <c r="L81" s="18">
+        <v>94.86</v>
+      </c>
+      <c r="M81" s="18">
+        <v>4727.8100000000004</v>
+      </c>
+      <c r="N81" s="44">
+        <v>484.1</v>
+      </c>
+      <c r="O81" s="44">
+        <v>75.905000000000001</v>
+      </c>
     </row>
     <row r="82" spans="1:15" ht="16.5" customHeight="1">
       <c r="A82" s="42"/>
@@ -35385,7 +35447,7 @@
     <row r="15" spans="1:2">
       <c r="A15" s="5" t="str">
         <f>Sheet1!O1</f>
-        <v xml:space="preserve">Silver </v>
+        <v>SIlver USD/Oz</v>
       </c>
       <c r="B15" s="34">
         <f>Sheet1!B69</f>
